--- a/DataTables/Datas/#VSWeaponLevel.xlsx
+++ b/DataTables/Datas/#VSWeaponLevel.xlsx
@@ -101,14 +101,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -564,148 +557,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1182,7 +1175,7 @@
         <v>1</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H4">
         <v>1</v>

--- a/DataTables/Datas/#VSWeaponLevel.xlsx
+++ b/DataTables/Datas/#VSWeaponLevel.xlsx
@@ -1,262 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="16760" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>weaponId</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>damage</t>
-  </si>
-  <si>
-    <t>cooldownSec</t>
-  </si>
-  <si>
-    <t>projSpeed</t>
-  </si>
-  <si>
-    <t>area</t>
-  </si>
-  <si>
-    <t>amount</t>
-  </si>
-  <si>
-    <t>durationSec</t>
-  </si>
-  <si>
-    <t>pierce</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>主键(武器id*100+等级)</t>
-  </si>
-  <si>
-    <t>武器id</t>
-  </si>
-  <si>
-    <t>等级</t>
-  </si>
-  <si>
-    <t>单次伤害</t>
-  </si>
-  <si>
-    <t>冷却(秒)</t>
-  </si>
-  <si>
-    <t>弹速(单位/秒)</t>
-  </si>
-  <si>
-    <t>范围系数</t>
-  </si>
-  <si>
-    <t>弹数</t>
-  </si>
-  <si>
-    <t>弹体存活时长(秒)</t>
-  </si>
-  <si>
-    <t>穿透数</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -557,153 +472,153 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -757,11 +672,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1048,374 +1026,2262 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O51"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>weaponId</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>damage</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>cooldownSec</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>projSpeed</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>durationSec</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>pierce</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>spreadDeg</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>orbitRadius</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>auraRadius</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>gravity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>主键(武器id*100+等级)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>武器id</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>单次伤害</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>冷却(秒)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>弹速(单位/秒)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>范围系数</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>弹数</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>弹体存活时长(秒)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>穿透数</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>扇形相邻弹夹角(度,0=同向散射用旧逻辑)</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>环绕半径(区域型Orbit用,0=不适用)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>光环半径(区域型Aura用,0=不适用)</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>重力加速度(单位/秒^2,0=直线弹道)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="n">
+        <v>101</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>102</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>103</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>104</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="E7" t="n">
+        <v>18</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>105</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="E8" t="n">
+        <v>22</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>106</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="E9" t="n">
+        <v>26</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>107</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="E10" t="n">
+        <v>30</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>108</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="E11" t="n">
+        <v>35</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G11" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
+      <c r="H11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>201</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>22</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>202</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>22</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>203</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G14" t="n">
+        <v>10</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>20</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>204</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>20</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>205</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>14</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G16" t="n">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="H16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>18</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>206</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>17</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>18</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>207</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>20</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G18" t="n">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="H18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>16</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>208</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>8</v>
+      </c>
+      <c r="E19" t="n">
+        <v>24</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G19" t="n">
+        <v>13</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>16</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>301</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>9</v>
+      </c>
+      <c r="L20" t="n">
+        <v>90</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>302</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>15</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>9</v>
+      </c>
+      <c r="L21" t="n">
+        <v>100</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>303</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>9</v>
+      </c>
+      <c r="L22" t="n">
+        <v>100</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>304</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>21</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>9</v>
+      </c>
+      <c r="L23" t="n">
+        <v>110</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>305</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>25</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>9</v>
+      </c>
+      <c r="L24" t="n">
+        <v>110</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>306</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" t="n">
+        <v>29</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>9</v>
+      </c>
+      <c r="L25" t="n">
+        <v>120</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>307</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>7</v>
+      </c>
+      <c r="E26" t="n">
+        <v>33</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>9</v>
+      </c>
+      <c r="L26" t="n">
+        <v>120</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>308</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" t="n">
+        <v>38</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>9</v>
+      </c>
+      <c r="L27" t="n">
+        <v>130</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>401</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>8</v>
+      </c>
+      <c r="K28" t="n">
+        <v>9</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>402</v>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>8</v>
+      </c>
+      <c r="K29" t="n">
+        <v>9</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>403</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>9</v>
+      </c>
+      <c r="K30" t="n">
+        <v>9</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>404</v>
+      </c>
+      <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>14</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>9</v>
+      </c>
+      <c r="K31" t="n">
+        <v>9</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>405</v>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>17</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>10</v>
+      </c>
+      <c r="K32" t="n">
+        <v>9</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>406</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>6</v>
+      </c>
+      <c r="E33" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>10</v>
+      </c>
+      <c r="K33" t="n">
+        <v>9</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>407</v>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" t="n">
+        <v>23</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>11</v>
+      </c>
+      <c r="K34" t="n">
+        <v>9</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>408</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="n">
+        <v>8</v>
+      </c>
+      <c r="E35" t="n">
+        <v>27</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" t="n">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="K35" t="n">
+        <v>9</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>501</v>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>9</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>502</v>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>9</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>503</v>
+      </c>
+      <c r="C38" t="n">
+        <v>5</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>9</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>504</v>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>6</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>9</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>505</v>
+      </c>
+      <c r="C40" t="n">
+        <v>5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" t="n">
+        <v>8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>9</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>506</v>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" t="n">
+        <v>10</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>9</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>507</v>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" t="n">
         <v>12</v>
       </c>
-      <c r="J2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="F42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>9</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>508</v>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" t="n">
+        <v>14</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>9</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>3</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>601</v>
+      </c>
+      <c r="C44" t="n">
+        <v>6</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>20</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K44" t="n">
+        <v>9</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" t="s">
+    <row r="45">
+      <c r="B45" t="n">
+        <v>602</v>
+      </c>
+      <c r="C45" t="n">
+        <v>6</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="n">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="2:11">
-      <c r="B4">
-        <v>101</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>10</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
+      <c r="F45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K45" t="n">
+        <v>9</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>603</v>
+      </c>
+      <c r="C46" t="n">
         <v>6</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11">
-      <c r="B5">
-        <v>102</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
-      </c>
-      <c r="E5">
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="n">
+        <v>28</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G46" t="n">
+        <v>6</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K46" t="n">
+        <v>9</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
         <v>12</v>
       </c>
-      <c r="F5">
-        <v>0.95</v>
-      </c>
-      <c r="G5">
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>604</v>
+      </c>
+      <c r="C47" t="n">
+        <v>6</v>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" t="n">
+        <v>33</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G47" t="n">
         <v>6.5</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11">
-      <c r="B6">
-        <v>103</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
+      <c r="H47" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2</v>
+      </c>
+      <c r="J47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K47" t="n">
+        <v>9</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>605</v>
+      </c>
+      <c r="C48" t="n">
+        <v>6</v>
+      </c>
+      <c r="D48" t="n">
+        <v>5</v>
+      </c>
+      <c r="E48" t="n">
+        <v>38</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G48" t="n">
+        <v>7</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2</v>
+      </c>
+      <c r="J48" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K48" t="n">
+        <v>9</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>606</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6</v>
+      </c>
+      <c r="D49" t="n">
+        <v>6</v>
+      </c>
+      <c r="E49" t="n">
+        <v>44</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K49" t="n">
+        <v>9</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>607</v>
+      </c>
+      <c r="C50" t="n">
+        <v>6</v>
+      </c>
+      <c r="D50" t="n">
+        <v>7</v>
+      </c>
+      <c r="E50" t="n">
+        <v>50</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G50" t="n">
+        <v>8</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I50" t="n">
         <v>3</v>
       </c>
-      <c r="E6">
-        <v>15</v>
-      </c>
-      <c r="F6">
-        <v>0.9</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2</v>
-      </c>
-      <c r="K6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11">
-      <c r="B7">
-        <v>104</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-      <c r="E7">
-        <v>18</v>
-      </c>
-      <c r="F7">
-        <v>0.85</v>
-      </c>
-      <c r="G7">
-        <v>7.5</v>
-      </c>
-      <c r="H7">
-        <v>1.1</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>2</v>
-      </c>
-      <c r="K7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11">
-      <c r="B8">
-        <v>105</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>5</v>
-      </c>
-      <c r="E8">
-        <v>22</v>
-      </c>
-      <c r="F8">
+      <c r="J50" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K50" t="n">
+        <v>9</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>608</v>
+      </c>
+      <c r="C51" t="n">
+        <v>6</v>
+      </c>
+      <c r="D51" t="n">
+        <v>8</v>
+      </c>
+      <c r="E51" t="n">
+        <v>58</v>
+      </c>
+      <c r="F51" t="n">
         <v>0.8</v>
       </c>
-      <c r="G8">
-        <v>8</v>
-      </c>
-      <c r="H8">
-        <v>1.2</v>
-      </c>
-      <c r="I8">
-        <v>2</v>
-      </c>
-      <c r="J8">
-        <v>2</v>
-      </c>
-      <c r="K8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11">
-      <c r="B9">
-        <v>106</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>6</v>
-      </c>
-      <c r="E9">
-        <v>26</v>
-      </c>
-      <c r="F9">
-        <v>0.75</v>
-      </c>
-      <c r="G9">
+      <c r="G51" t="n">
         <v>8.5</v>
       </c>
-      <c r="H9">
-        <v>1.3</v>
-      </c>
-      <c r="I9">
-        <v>2</v>
-      </c>
-      <c r="J9">
-        <v>2</v>
-      </c>
-      <c r="K9">
+      <c r="H51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I51" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="2:11">
-      <c r="B10">
-        <v>107</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>7</v>
-      </c>
-      <c r="E10">
-        <v>30</v>
-      </c>
-      <c r="F10">
-        <v>0.7</v>
-      </c>
-      <c r="G10">
-        <v>9</v>
-      </c>
-      <c r="H10">
-        <v>1.4</v>
-      </c>
-      <c r="I10">
-        <v>3</v>
-      </c>
-      <c r="J10">
-        <v>2</v>
-      </c>
-      <c r="K10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11">
-      <c r="B11">
-        <v>108</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>8</v>
-      </c>
-      <c r="E11">
-        <v>35</v>
-      </c>
-      <c r="F11">
-        <v>0.65</v>
-      </c>
-      <c r="G11">
-        <v>10</v>
-      </c>
-      <c r="H11">
-        <v>1.5</v>
-      </c>
-      <c r="I11">
-        <v>3</v>
-      </c>
-      <c r="J11">
-        <v>2</v>
-      </c>
-      <c r="K11">
-        <v>3</v>
+      <c r="J51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K51" t="n">
+        <v>9</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>